--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-dispense.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-dispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -445,6 +445,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -484,6 +494,10 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -494,6 +508,9 @@
   </si>
   <si>
     <t>CombinedMedicationDispense.id</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -509,6 +526,13 @@
     <t>The procedure that trigger the dispense.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -604,6 +628,9 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
@@ -774,6 +801,9 @@
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
@@ -881,6 +911,13 @@
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
+  </si>
+  <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.quantity</t>
@@ -995,6 +1032,9 @@
   </si>
   <si>
     <t>Extra information about the dispense that could not be conveyed in the other attributes.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1514,7 +1554,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2543,19 +2583,19 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2567,7 +2607,7 @@
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2587,10 +2627,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2616,16 +2656,16 @@
         <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2662,19 +2702,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2686,7 +2726,7 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2706,10 +2746,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2732,16 +2772,16 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2791,7 +2831,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2800,33 +2840,33 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2849,15 +2889,17 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
@@ -2906,7 +2948,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2915,16 +2957,16 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2938,10 +2980,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2967,13 +3009,13 @@
         <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2981,7 +3023,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>78</v>
@@ -2999,31 +3041,31 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Z13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
@@ -3038,16 +3080,16 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3055,10 +3097,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3081,13 +3123,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3114,13 +3156,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3138,7 +3180,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3147,16 +3189,16 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>78</v>
@@ -3170,10 +3212,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3196,16 +3238,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3234,10 +3276,10 @@
         <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3255,7 +3297,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3264,7 +3306,7 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>100</v>
@@ -3273,7 +3315,7 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3282,15 +3324,15 @@
         <v>78</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3313,16 +3355,16 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3372,7 +3414,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3381,33 +3423,33 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3430,16 +3472,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3489,7 +3531,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3498,33 +3540,33 @@
         <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3547,15 +3589,17 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3604,7 +3648,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3613,16 +3657,16 @@
         <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3636,10 +3680,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3662,15 +3706,17 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3719,7 +3765,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3728,19 +3774,19 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3751,10 +3797,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3777,13 +3823,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3834,7 +3880,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3843,16 +3889,16 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3866,10 +3912,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3892,13 +3938,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3949,7 +3995,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3967,7 +4013,7 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
@@ -3981,10 +4027,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4013,7 +4059,7 @@
         <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -4054,19 +4100,19 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4078,13 +4124,13 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4098,14 +4144,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4127,16 +4173,16 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4185,7 +4231,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4197,7 +4243,7 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4217,10 +4263,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4243,17 +4289,19 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4278,13 +4326,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -4302,7 +4350,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4311,7 +4359,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4320,7 +4368,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4329,15 +4377,15 @@
         <v>78</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4360,15 +4408,17 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4417,7 +4467,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -4426,16 +4476,16 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4449,10 +4499,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4475,15 +4525,17 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4532,7 +4584,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4541,16 +4593,16 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4564,10 +4616,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4590,16 +4642,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4649,7 +4701,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4658,33 +4710,33 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4707,15 +4759,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4740,13 +4794,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4764,7 +4818,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4773,7 +4827,7 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -4782,24 +4836,24 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4822,15 +4876,17 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4879,7 +4935,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4888,33 +4944,33 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>288</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4937,15 +4993,17 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -4994,7 +5052,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5003,16 +5061,16 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>288</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5021,15 +5079,15 @@
         <v>78</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5052,13 +5110,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5109,7 +5167,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5127,24 +5185,24 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5167,13 +5225,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5224,7 +5282,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5239,27 +5297,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5282,15 +5340,17 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5339,7 +5399,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5348,33 +5408,33 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5397,15 +5457,17 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5454,7 +5516,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5463,22 +5525,22 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -5486,10 +5548,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5512,15 +5574,17 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5569,7 +5633,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5578,16 +5642,16 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5596,15 +5660,15 @@
         <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5627,16 +5691,16 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5686,7 +5750,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5704,7 +5768,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -5718,10 +5782,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5744,13 +5808,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5801,7 +5865,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5810,7 +5874,7 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
@@ -5819,13 +5883,13 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -5833,10 +5897,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5859,13 +5923,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5916,7 +5980,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5934,7 +5998,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -5948,10 +6012,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5980,7 +6044,7 @@
         <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>137</v>
@@ -6021,19 +6085,19 @@
         <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6045,13 +6109,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6065,14 +6129,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6094,16 +6158,16 @@
         <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6152,7 +6216,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6164,7 +6228,7 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -6184,10 +6248,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6210,13 +6274,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6267,7 +6331,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>88</v>
@@ -6285,7 +6349,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6299,10 +6363,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6325,15 +6389,17 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6358,13 +6424,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6382,7 +6448,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6391,7 +6457,7 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
@@ -6400,24 +6466,24 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6440,15 +6506,17 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6473,13 +6541,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6497,7 +6565,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6506,7 +6574,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -6515,24 +6583,24 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6555,15 +6623,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6612,7 +6682,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6621,22 +6691,22 @@
         <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6644,14 +6714,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6670,16 +6740,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6729,7 +6799,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6738,16 +6808,16 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6761,10 +6831,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6787,16 +6857,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6846,7 +6916,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6855,16 +6925,16 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-dispense.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-dispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -445,16 +445,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -494,10 +484,6 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -508,9 +494,6 @@
   </si>
   <si>
     <t>CombinedMedicationDispense.id</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -526,13 +509,6 @@
     <t>The procedure that trigger the dispense.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -628,9 +604,6 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
@@ -801,9 +774,6 @@
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
@@ -911,13 +881,6 @@
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.quantity</t>
@@ -1032,9 +995,6 @@
   </si>
   <si>
     <t>Extra information about the dispense that could not be conveyed in the other attributes.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1554,7 +1514,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2583,19 +2543,19 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2607,7 +2567,7 @@
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2627,10 +2587,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2656,16 +2616,16 @@
         <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2702,19 +2662,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2726,7 +2686,7 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2746,10 +2706,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2772,16 +2732,16 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2831,7 +2791,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2840,33 +2800,33 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2889,17 +2849,15 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
@@ -2948,7 +2906,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2957,16 +2915,16 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2980,10 +2938,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3009,13 +2967,13 @@
         <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3023,7 +2981,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>78</v>
@@ -3041,13 +2999,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3065,7 +3023,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>88</v>
@@ -3080,16 +3038,16 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -3097,10 +3055,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3123,13 +3081,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3156,13 +3114,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3180,7 +3138,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3189,16 +3147,16 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>78</v>
@@ -3212,10 +3170,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3238,16 +3196,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3276,10 +3234,10 @@
         <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3297,7 +3255,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3306,7 +3264,7 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>100</v>
@@ -3315,7 +3273,7 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3324,15 +3282,15 @@
         <v>78</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3355,16 +3313,16 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3414,7 +3372,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3423,33 +3381,33 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3472,16 +3430,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3531,7 +3489,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3540,33 +3498,33 @@
         <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3589,17 +3547,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -3648,7 +3604,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3657,16 +3613,16 @@
         <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3680,10 +3636,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3706,17 +3662,15 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3765,7 +3719,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3774,19 +3728,19 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3797,10 +3751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3823,13 +3777,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3880,7 +3834,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3889,16 +3843,16 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3912,10 +3866,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3938,13 +3892,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3995,7 +3949,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4013,7 +3967,7 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
@@ -4027,10 +3981,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4059,7 +4013,7 @@
         <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -4100,19 +4054,19 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4124,13 +4078,13 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4144,14 +4098,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4173,16 +4127,16 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4231,7 +4185,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4243,7 +4197,7 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4263,10 +4217,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4289,19 +4243,17 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4326,13 +4278,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -4350,7 +4302,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4359,7 +4311,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4368,7 +4320,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4377,15 +4329,15 @@
         <v>78</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4408,17 +4360,15 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4467,7 +4417,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -4476,16 +4426,16 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4499,10 +4449,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4525,17 +4475,15 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4584,7 +4532,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4593,16 +4541,16 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4616,10 +4564,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4642,16 +4590,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4701,7 +4649,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4710,33 +4658,33 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4759,17 +4707,15 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4794,13 +4740,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4818,7 +4764,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4827,7 +4773,7 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
@@ -4836,24 +4782,24 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4876,17 +4822,15 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4935,7 +4879,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4944,33 +4888,33 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>288</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4993,17 +4937,15 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5052,7 +4994,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5061,16 +5003,16 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>288</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5079,15 +5021,15 @@
         <v>78</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5110,13 +5052,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5167,7 +5109,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5185,24 +5127,24 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5225,13 +5167,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5282,7 +5224,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5297,27 +5239,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5340,17 +5282,15 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5399,7 +5339,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5408,33 +5348,33 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5457,17 +5397,15 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5516,7 +5454,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5525,22 +5463,22 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -5548,10 +5486,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5574,17 +5512,15 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5633,7 +5569,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5642,16 +5578,16 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5660,15 +5596,15 @@
         <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5691,16 +5627,16 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5750,7 +5686,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5768,7 +5704,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -5782,10 +5718,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5808,13 +5744,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5865,7 +5801,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5874,7 +5810,7 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
@@ -5883,13 +5819,13 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -5897,10 +5833,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5923,13 +5859,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5980,7 +5916,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5998,7 +5934,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6012,10 +5948,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6044,7 +5980,7 @@
         <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>137</v>
@@ -6085,19 +6021,19 @@
         <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6109,13 +6045,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6129,14 +6065,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6158,16 +6094,16 @@
         <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>137</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6216,7 +6152,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6228,7 +6164,7 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -6248,10 +6184,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6274,13 +6210,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6331,7 +6267,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>88</v>
@@ -6349,7 +6285,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6363,10 +6299,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6389,17 +6325,15 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6424,13 +6358,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6448,7 +6382,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6457,7 +6391,7 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
@@ -6466,24 +6400,24 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6506,17 +6440,15 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6541,13 +6473,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6565,7 +6497,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6574,7 +6506,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -6583,24 +6515,24 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6623,17 +6555,15 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6682,7 +6612,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6691,22 +6621,22 @@
         <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6714,14 +6644,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6740,16 +6670,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6799,7 +6729,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6808,16 +6738,16 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6831,10 +6761,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,16 +6787,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6916,7 +6846,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6925,16 +6855,16 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
